--- a/doc/ProductBacklog_group38.xlsx
+++ b/doc/ProductBacklog_group38.xlsx
@@ -1279,7 +1279,7 @@
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
